--- a/pseudodata/1011.xlsx
+++ b/pseudodata/1011.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -536,28 +536,28 @@
         <v>0.1</v>
       </c>
       <c r="I2" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0005148809411207802</v>
+        <v>0.0002048600017658673</v>
       </c>
       <c r="M2" t="n">
-        <v>7.507501735032484e-05</v>
+        <v>0.001616362484156185</v>
       </c>
       <c r="N2" t="n">
-        <v>2.574404705603901e-05</v>
+        <v>1.024300008829336e-05</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -590,28 +590,28 @@
         <v>0.1</v>
       </c>
       <c r="I3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005531434465741898</v>
+        <v>0.0001815240846669416</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0001011998275819507</v>
+        <v>0.001646147115230871</v>
       </c>
       <c r="N3" t="n">
-        <v>2.765717232870949e-05</v>
+        <v>9.076204233347079e-06</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -644,28 +644,28 @@
         <v>0.1</v>
       </c>
       <c r="I4" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0004207708466985396</v>
+        <v>0.0001356720240446564</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0001426541016838549</v>
+        <v>0.001800791856675498</v>
       </c>
       <c r="N4" t="n">
-        <v>2.103854233492698e-05</v>
+        <v>6.783601202232819e-06</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -698,28 +698,28 @@
         <v>0.1</v>
       </c>
       <c r="I5" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L5" t="n">
-        <v>0.000195066865504116</v>
+        <v>6.925304189431206e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0002033464081590957</v>
+        <v>0.002095536135371545</v>
       </c>
       <c r="N5" t="n">
-        <v>9.7533432752058e-06</v>
+        <v>3.462652094715603e-06</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -752,28 +752,28 @@
         <v>0.1</v>
       </c>
       <c r="I6" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L6" t="n">
-        <v>-8.367750651561678e-05</v>
+        <v>-1.488895647091454e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0002896685109093281</v>
+        <v>0.002565267446201983</v>
       </c>
       <c r="N6" t="n">
-        <v>-4.183875325780839e-06</v>
+        <v>-7.444478235457272e-07</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -806,28 +806,28 @@
         <v>0.1</v>
       </c>
       <c r="I7" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.000383060575185077</v>
+        <v>-0.000110454193613701</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0004017014439893911</v>
+        <v>0.003262410335643286</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.915302875925385e-05</v>
+        <v>-5.52270968068505e-06</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -860,28 +860,28 @@
         <v>0.1</v>
       </c>
       <c r="I8" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.00064476097071267</v>
+        <v>-0.0002060229895529169</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0005296758654512603</v>
+        <v>0.004255709538299734</v>
       </c>
       <c r="N8" t="n">
-        <v>-3.223804853563351e-05</v>
+        <v>-1.030114947764584e-05</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -908,34 +908,34 @@
         <v>0.5</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="H9" t="n">
         <v>0.1</v>
       </c>
       <c r="I9" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L9" t="n">
-        <v>4.785766209016035e-05</v>
+        <v>-0.0002848026375878743</v>
       </c>
       <c r="M9" t="n">
-        <v>7.507501735032484e-05</v>
+        <v>0.005630999604606608</v>
       </c>
       <c r="N9" t="n">
-        <v>2.392883104508018e-06</v>
+        <v>-1.424013187939372e-05</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -962,34 +962,34 @@
         <v>0.5</v>
       </c>
       <c r="G10" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="H10" t="n">
         <v>0.1</v>
       </c>
       <c r="I10" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0001612530544044314</v>
+        <v>-0.0003259749688812096</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0001011998275819507</v>
+        <v>0.007493733658936986</v>
       </c>
       <c r="N10" t="n">
-        <v>8.06265272022157e-06</v>
+        <v>-1.629874844406048e-05</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -1016,34 +1016,34 @@
         <v>0.5</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>6.5</v>
       </c>
       <c r="H11" t="n">
         <v>0.1</v>
       </c>
       <c r="I11" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0002137284935795153</v>
+        <v>-0.0003087085067055127</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0001426541016838549</v>
+        <v>0.009959836592124023</v>
       </c>
       <c r="N11" t="n">
-        <v>1.068642467897576e-05</v>
+        <v>-1.543542533527564e-05</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -1070,34 +1070,34 @@
         <v>0.5</v>
       </c>
       <c r="G12" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="H12" t="n">
         <v>0.1</v>
       </c>
       <c r="I12" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0002059830310863229</v>
+        <v>-0.0002201316738730216</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0002033464081590957</v>
+        <v>0.01310644590118565</v>
       </c>
       <c r="N12" t="n">
-        <v>1.029915155431615e-05</v>
+        <v>-1.100658369365108e-05</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -1124,34 +1124,34 @@
         <v>0.5</v>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="H13" t="n">
         <v>0.1</v>
       </c>
       <c r="I13" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0001542527260848044</v>
+        <v>-6.085910510374354e-05</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0002896685109093281</v>
+        <v>0.01688631264013874</v>
       </c>
       <c r="N13" t="n">
-        <v>7.712636304240218e-06</v>
+        <v>-3.042955255187177e-06</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -1178,34 +1178,34 @@
         <v>0.5</v>
       </c>
       <c r="G14" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="H14" t="n">
         <v>0.1</v>
       </c>
       <c r="I14" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L14" t="n">
-        <v>7.896618600072113e-05</v>
+        <v>0.0001691152499128881</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0004017014439893911</v>
+        <v>0.02113204400307453</v>
       </c>
       <c r="N14" t="n">
-        <v>3.948309300036057e-06</v>
+        <v>8.455762495644406e-06</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -1232,34 +1232,34 @@
         <v>0.5</v>
       </c>
       <c r="G15" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="H15" t="n">
         <v>0.1</v>
       </c>
       <c r="I15" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L15" t="n">
-        <v>1.524234491050779e-06</v>
+        <v>0.0004965919765267876</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0005296758654512603</v>
+        <v>0.02579037950358577</v>
       </c>
       <c r="N15" t="n">
-        <v>7.621172455253894e-08</v>
+        <v>2.482959882633938e-05</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -1286,34 +1286,34 @@
         <v>0.5</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H16" t="n">
         <v>0.1</v>
       </c>
       <c r="I16" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.483271534042054e-05</v>
+        <v>0.0009636365821541357</v>
       </c>
       <c r="M16" t="n">
-        <v>7.507501735032484e-05</v>
+        <v>0.03115192973471654</v>
       </c>
       <c r="N16" t="n">
-        <v>-7.416357670210269e-07</v>
+        <v>4.818182910770678e-05</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -1340,34 +1340,34 @@
         <v>0.5</v>
       </c>
       <c r="G17" t="n">
-        <v>2.5</v>
+        <v>9.5</v>
       </c>
       <c r="H17" t="n">
         <v>0.1</v>
       </c>
       <c r="I17" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L17" t="n">
-        <v>-4.292808605376939e-06</v>
+        <v>0.001569211868426151</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0001011998275819507</v>
+        <v>0.03768770019189761</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.14640430268847e-07</v>
+        <v>7.846059342130757e-05</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -1394,253 +1394,37 @@
         <v>0.5</v>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H18" t="n">
         <v>0.1</v>
       </c>
       <c r="I18" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L18" t="n">
-        <v>2.229327991201954e-05</v>
+        <v>0.002212532742392742</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0001426541016838549</v>
+        <v>0.0455244215780122</v>
       </c>
       <c r="N18" t="n">
-        <v>1.114663995600977e-06</v>
+        <v>0.0001106266371196371</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="n">
-        <v>100</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I19" t="n">
-        <v>50</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>100</v>
-      </c>
-      <c r="L19" t="n">
-        <v>6.284798340396882e-05</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.0002033464081590957</v>
-      </c>
-      <c r="N19" t="n">
-        <v>3.142399170198441e-06</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="n">
-        <v>100</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G20" t="n">
-        <v>4</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I20" t="n">
-        <v>50</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>100</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0.0001100010840951743</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0.0002896685109093281</v>
-      </c>
-      <c r="N20" t="n">
-        <v>5.500054204758716e-06</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" t="n">
-        <v>100</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I21" t="n">
-        <v>50</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>100</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.0001512758747573619</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.0004017014439893911</v>
-      </c>
-      <c r="N21" t="n">
-        <v>7.563793737868094e-06</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" t="n">
-        <v>100</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G22" t="n">
-        <v>5</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I22" t="n">
-        <v>50</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>100</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0.0001865556963516443</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0.0005296758654512603</v>
-      </c>
-      <c r="N22" t="n">
-        <v>9.327784817582217e-06</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P22" t="n">
         <v>1</v>
       </c>
     </row>
